--- a/source_data/workbooks/Source_Data_ED_Fig4.xlsx
+++ b/source_data/workbooks/Source_Data_ED_Fig4.xlsx
@@ -140,10 +140,10 @@
     <t>round 20 selected</t>
   </si>
   <si>
-    <t>LOO pearson</t>
+    <t>Selected (Train LOO Pearson r)</t>
   </si>
   <si>
-    <t>test pearson</t>
+    <t>Test Pearson r</t>
   </si>
   <si>
     <t>answered</t>
@@ -167,10 +167,10 @@
     <t>Human Workflow C</t>
   </si>
   <si>
-    <t>TITAN Linear Probe</t>
+    <t>TITAN LinearProbe</t>
   </si>
   <si>
-    <t>TITAN Fine-tune</t>
+    <t>TITAN FineTune</t>
   </si>
   <si>
     <t>MUSK ABMIL</t>
@@ -1893,7 +1893,7 @@
     <col min="3" max="3" width="44.7109375" customWidth="1"/>
     <col min="4" max="4" width="37.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="10" width="12.7109375" customWidth="1"/>
